--- a/frontend/Book1.xlsx
+++ b/frontend/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohin\Desktop\mailer\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81189BE-E1D9-4452-A348-5B4633E262D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168E5C4C-9C4A-4E1C-8A3B-0A266AB74E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{27EAA458-7748-41F8-B3E3-EBDD6077E138}"/>
   </bookViews>
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC00934F-2C0D-40E3-AAEF-88A434EA25B5}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="44.81640625" customWidth="1"/>
@@ -529,6 +529,11 @@
       </c>
       <c r="C7" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
